--- a/esyluban/examples/dev/DataTables/l10n/Demo.xlsx
+++ b/esyluban/examples/dev/DataTables/l10n/Demo.xlsx
@@ -1086,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="l10n.TbL10NDemo" &amp; value_type="l10n.L10NDemo" &amp; read_schema_from_file="false" &amp; input="l10n/Demo.xlsx" &amp; output="l10n_tbl10ndemo"</t>
+          <t>full_name="l10n.TbL10NDemo" &amp; input="l10n/Demo.xlsx"</t>
         </is>
       </c>
     </row>
@@ -1231,44 +1231,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
